--- a/information_request_forms/027_document_retention_review_request_form--information_request_forms.xlsx
+++ b/information_request_forms/027_document_retention_review_request_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'employee',_'value':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Employee', 'value': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'review',_'value':_'review'}</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Review', 'value': 'Review'}</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'retention',_'value':_'retention'}</t>
+          <t>retention</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Retention', 'value': 'Retention'}</t>
+          <t>Retention</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'request',_'value':_'request'}</t>
+          <t>request</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Request', 'value': 'Request'}</t>
+          <t>Request</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'supervisor',_'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Supervisor', 'value': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'contract',_'value':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Contract', 'value': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'agreement',_'value':_'agreement'}</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Agreement', 'value': 'Agreement'}</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'record',_'value':_'record'}</t>
+          <t>record</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Record', 'value': 'Record'}</t>
+          <t>Record</t>
         </is>
       </c>
     </row>
